--- a/data/en.xlsx
+++ b/data/en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13000"/>
+    <workbookView windowHeight="23860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -388,7 +388,7 @@
   </si>
   <si>
     <t>你好，我叫麦琪，来自美国。我的问题是：你家是什么样的？
-嗯，先说一下吧，我住的是公寓，住在一楼。楼里有电梯，不过我不用。我的公寓有 2 间卧室和 2 个卫生间，还有一个厨房和一间很大的客厅。家里我最喜欢的地方是露台，它在室外。我喜欢坐在外面的露台上喝咖啡。
+嗯，我先说下我住的是公寓。我的公寓在一楼。楼里有电梯，不过我不用。我的公寓有 2 间卧室和 2 个卫生间，还有一个厨房和一间很大的客厅。家里我最喜欢的地方是露台，它在室外。我喜欢坐在外面的露台上喝咖啡。
 你家是什么样的？</t>
   </si>
   <si>
@@ -630,7 +630,7 @@
   </si>
   <si>
     <t>你好，我叫美优。我来自日本。我的问题是，谁在上学？
-我侄子在上学。他叫米奇，13 岁，上初中。学校就在湖边。米奇特别喜欢弹钢琴，他在班里弹钢琴，弹得特别好，拿过很多奖。米奇有个妹妹，没有兄弟。他妹妹也在上学。
+我侄子在上学。他叫米奇，13 岁，上初中。学校就在湖边。米奇特别喜欢弹钢琴，他在班里弹钢琴，弹得特别好，拿过很多奖。米奇有个妹妹。他没有兄弟。他妹妹也在上学。
 你上学吗？</t>
   </si>
   <si>
@@ -638,7 +638,7 @@
   </si>
   <si>
     <t>Hello, my name is Kyle. I am from the UK. My question for you today is what do you do on your lunch break?
-What do you do on your lunch break? I go on my phone, I eat my lunch. I rest.
+I go on my phone, I eat my lunch. I rest.
 What do you do on your lunch break?</t>
   </si>
   <si>
@@ -668,7 +668,7 @@
   </si>
   <si>
     <t>你好，我叫美优。我来自日本。我的问题是，你的家人来自哪里？
-我妈妈来自大阪。大阪在日本西部，是一座大城市。我爸爸来自横滨。横滨也在日本，离东京不远。东京是日本的首都。我丈夫不是日本人，他来自罗马尼亚。我和丈夫住在布加勒斯特。布加勒斯特是罗马尼亚的首都。我不住在日本。
+我妈妈来自大阪。大阪在日本。在日本西部，是一座大城市。我爸爸来自横滨。横滨也在日本，离东京不远。东京是日本的首都。我丈夫不是日本人，他来自罗马尼亚。我和丈夫住在布加勒斯特。布加勒斯特是罗马尼亚的首都。我不住在日本。
 你家人来自哪里？</t>
   </si>
   <si>
@@ -5289,11 +5289,11 @@
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36" style="1" customWidth="1"/>
-    <col min="3" max="3" width="100" style="1" customWidth="1"/>
-    <col min="4" max="4" width="42" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7307692307692" style="2" customWidth="1"/>
-    <col min="6" max="6" width="111.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.2307692307692" style="1" customWidth="1"/>
+    <col min="3" max="3" width="93.1153846153846" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5865384615385" style="2" customWidth="1"/>
+    <col min="6" max="6" width="79.6153846153846" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:6">

--- a/data/en.xlsx
+++ b/data/en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23860"/>
+    <workbookView windowWidth="29100" windowHeight="13000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -842,7 +842,7 @@
     <t>What desserts do you like?</t>
   </si>
   <si>
-    <t>Hello, my name is Kyle. I am from the UK and my question for you today is, what desserts do you like? What desserts do you like?
+    <t>Hello, my name is Kyle. I am from the UK and my question for you today is, what desserts do you like? 
 I like cheesecake. I like brownies. I like ice cream. I don't like mouse. I don't like tiramisu. I don't like custard.
 What desserts do you like?</t>
   </si>
@@ -853,7 +853,7 @@
     <t>你喜欢什么甜点？</t>
   </si>
   <si>
-    <t>你好，我叫凯尔。我来自英国。我的问题是，你喜欢什么甜点？
+    <t>你好，我叫凯尔。我来自英国，我的问题是，你喜欢什么甜点？
 我喜欢芝士蛋糕。我喜欢布朗尼。我喜欢冰淇淋。我不喜欢慕斯。我不喜欢提拉米苏。我不喜欢卡仕达酱。
 你喜欢什么甜点？</t>
   </si>
@@ -6316,7 +6316,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="52" ht="26.4" customHeight="1" spans="1:6">
+    <row r="52" ht="127" customHeight="1" spans="1:6">
       <c r="A52" s="7" t="s">
         <v>253</v>
       </c>
